--- a/LetzRyd_Forms_Registry.xlsx
+++ b/LetzRyd_Forms_Registry.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forms Registry" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,14 +29,21 @@
       <name val="Inter"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Inter"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Inter"/>
+      <color rgb="001A1A2E"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -49,8 +56,20 @@
         <bgColor rgb="000A1650"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001AB394"/>
+        <bgColor rgb="001AB394"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -60,29 +79,47 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00BBBBBB"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00BBBBBB"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00BBBBBB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00BBBBBB"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DEDEDE"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DEDEDE"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DEDEDE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DEDEDE"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,2668 +486,2821 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="69" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>LetzRyd Portal — Forms Variable Registry</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
           <t>Form Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Variable/Field Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Display Label</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Input Type / Block</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Choices / Options</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Walkin Form</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Event_date</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>📅 date of visit</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Date of visit</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Date Picker</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Walkin Form</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>City_id</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>🏙️ city</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Selector (Dropdown)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Dynamic (from DB)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Walkin Form</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Attending_executive_user_id</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>👤 attending executive</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Attending executive</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Selector (Dropdown)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Dynamic (from DB)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Walkin Form</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Partner_name</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>👤 partner / driver name</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Partner / driver name</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Walkin Form</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Partner_number</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>📞 partner phone number</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Partner phone number</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Tel)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Walkin Form</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Dl_number</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>🪪 driving license (dl) number</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Walkin Form</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Visiting_reason</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>❓ reason for visit</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Reason for visit</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Selector (Dropdown)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>["New Joining", "Car Return", "Inquiry", "Payment Issue", "Other"]</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Walkin Form</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>📝 remarks</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Event_date</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>📅 date of onboarding</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Date of onboarding</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Date Picker</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Driver_name</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>👤 driver name</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Driver name</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Father_name</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>👤 father name</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Father name</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Dob</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>🎂 date of birth</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Date of birth</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Date Picker</t>
         </is>
       </c>
-      <c r="E13" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Driver_phone</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>📞 driver phone number</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Driver phone number</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Tel)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Whatsapp_number</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>💬 whatsapp number</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Whatsapp number</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Tel)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Email_address</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>✉️ email address</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Email address</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Email)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Emergency_name</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>👤 emergency contact name</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Emergency contact name</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Emergency_phone</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>📞 emergency contact phone</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Emergency contact phone</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Tel)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Reference_name</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>👤 reference name</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Reference name</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Reference_number</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>📞 reference phone number</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Reference phone number</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Tel)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Address_as_per_aadhaar</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>🏠 permanent address (aadhaar)</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Permanent address (aadhaar)</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Present_address</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>🏠 present address</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Present address</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Pan_number</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>💳 pan card number</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Pan card number</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Aadhaar_number</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>💳 aadhaar card number</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Aadhaar card number</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Dl_number</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>🪪 driving license (dl) number</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E25" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Dl_expiry_date</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>📅 dl expiry date</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Dl expiry date</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Date Picker</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Selfie_url</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>📸 driver selfie</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Driver selfie</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Photo/File Upload</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Image (JPEG/PNG)</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Pan_card_url</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>📸 pan card front photo</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Pan card front photo</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Photo/File Upload</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>Image (JPEG/PNG)</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Aadhaar_front_url</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>📸 aadhaar card front photo</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Aadhaar card front photo</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>Photo/File Upload</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>Image (JPEG/PNG)</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Aadhaar_back_url</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>📸 aadhaar card back photo</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Aadhaar card back photo</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Photo/File Upload</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>Image (JPEG/PNG)</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Dl_front_url</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>📸 driving license front photo</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Driving license front photo</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Photo/File Upload</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Image (JPEG/PNG)</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Dl_back_url</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>📸 driving license back photo</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Driving license back photo</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Photo/File Upload</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>Image (JPEG/PNG)</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Address_proof_url</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>📸 present address proof (rent/elec)</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Present address proof (rent/elec)</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Photo/File Upload</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>Image/PDF</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Pan_aadhaar_linked</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>🔗 pan - aadhaar linked?</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Pan - aadhaar linked?</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Selector (Radio)</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>["Yes", "No"]</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Pan_aadhaar_link_photo_url</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>📸 pan-aadhaar link proof (if no)</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Pan-aadhaar link proof (if no)</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>Photo/File Upload</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>Image/PDF</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Bank_account_name</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>👤 bank account holder name</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Bank account holder name</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>Account_no</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>🔢 bank account number</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Bank account number</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Onboarding Form</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Ifsc_code</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>🏦 bank ifsc code</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Bank ifsc code</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E38" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Allocation_date</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>📅 date of allocation</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Date of allocation</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>Date Picker</t>
         </is>
       </c>
-      <c r="E39" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Allocation_type</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>🔄 allocation type</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Allocation type</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>Selector (Radio)</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>["New Allocation", "Car Swap", "Reallocation"]</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>City_name</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>🏙️ city</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>Selector (Dropdown)</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>Dynamic (from DB)</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Driver_id</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>🆔 operator / driver id</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Operator / driver id</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E42" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Driver_name</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>👤 driver name</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Driver name</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E43" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Driver_phone</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>📞 driver phone number</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Driver phone number</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Tel)</t>
         </is>
       </c>
-      <c r="E44" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>Vehicle_number</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>🚗 vehicle number</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Vehicle number</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E45" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Rental_plan</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>📋 rental plan</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Rental plan</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>Selector (Dropdown)</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>Dynamic (from DB)</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Security_deposit</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>💰 security deposit paid (inr)</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Security deposit paid (inr)</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Number)</t>
         </is>
       </c>
-      <c r="E47" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Car_cleaning</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>🧹 car cleaning status</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Car cleaning status</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>Selector (Radio)</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>["Clean", "Dirty"]</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Fuel_level</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>⛽ fuel level (%)</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Fuel level (%)</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Number)</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>0 - 100</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Odometer_reading</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>📊 odometer reading (km)</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Odometer reading (km)</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Number)</t>
         </is>
       </c>
-      <c r="E50" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>Odometer_photo_url</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>📸 odometer photo</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Odometer photo</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>Photo/File Upload</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>Image</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Car_photos_url</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>📸 car photos (minimum 4)</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Car photos (minimum 4)</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>Photo/File Upload</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>Multiple Images</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>Pdi_remarks</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>📝 pdi remarks / scratches</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Pdi remarks / scratches</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E53" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Signed_contract_url</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>✍️ signed contract</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Signed contract</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>Photo/File Upload</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>PDF/Image</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Drop_off_date</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>📅 date of dropoff / return</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Date of dropoff / return</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>Date Picker</t>
         </is>
       </c>
-      <c r="E55" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Drop_off_odometer</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>📊 return odometer reading (km)</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Return odometer reading (km)</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Number)</t>
         </is>
       </c>
-      <c r="E56" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="E57" s="4" t="n"/>
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>Drop_off_odometer_photo</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>📸 return odometer photo</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Return odometer photo</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>Photo/File Upload</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>Image</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Allocation &amp; Drop-off Form</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Drop_off_car_photos</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>📸 return car photos</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Return car photos</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>Photo/File Upload</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>Multiple Images</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Adjustment Form</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>Event_date</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>📅 date of adjustment</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Date of adjustment</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>Date Picker</t>
         </is>
       </c>
-      <c r="E59" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="E60" s="4" t="n"/>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Adjustment Form</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>City_name</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>🏙️ city</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>Selector (Dropdown)</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>["Bengaluru", "Mumbai"]</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>Adjustment Form</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Driver_id</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>🆔 operator / driver id</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Operator / driver id</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E61" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="E62" s="4" t="n"/>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Adjustment Form</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Driver_name</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>👤 driver name</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Driver name</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E62" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>Adjustment Form</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>Adjustment_type</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>🔄 adjustment type</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>Adjustment type</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>Selector (Radio)</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>["Credit (Payment to Partner)", "Debit (Deduction from Partner)"]</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Adjustment Form</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>📁 adjustment category</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Adjustment category</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>Selector (Dropdown)</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>Dynamic (by City/Type)</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>Adjustment Form</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>💵 amount (inr)</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Amount (inr)</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Number)</t>
         </is>
       </c>
-      <c r="E65" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>Adjustment Form</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>📝 detailed remarks</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Detailed remarks</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E66" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>Adjustment Form</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>Approval_proof_url</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>📎 approval proof</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Approval proof</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>Photo/File Upload</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>Image/PDF</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>Adjustment Form</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>Approved_by</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>👤 approved by (name)</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Approved by (name)</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E68" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>Adjustment Form</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>Accident_deductions</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>🚗 accident deductions applicable?</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Accident deductions applicable?</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>Selector (Radio)</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>["Yes", "No"]</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>Adjustment Form</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>Accident_amount</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>💵 accident amount</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Accident amount</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Number)</t>
         </is>
       </c>
-      <c r="E70" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="E71" s="4" t="n"/>
+      <c r="F71" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>Adjustment Form</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>Accident_proof_url</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>📎 accident proof / gd</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Accident proof / gd</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>Photo/File Upload</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t>Image/PDF</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>Adjustment Form</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>Challan_deductions</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>🚨 challan deductions applicable?</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Challan deductions applicable?</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>Selector (Radio)</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="4" t="inlineStr">
         <is>
           <t>["Yes", "No"]</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>Adjustment Form</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>Challan_amount</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>💵 challan amount</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Challan amount</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Number)</t>
         </is>
       </c>
-      <c r="E73" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="E74" s="4" t="n"/>
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>Adjustment Form</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>Challan_proof_url</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>📎 challan proof</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Challan proof</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>Photo/File Upload</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>PDF/Image</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>Adjustment Form</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>Submitting_user</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>🔑 submitted by (user)</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Submitted by (user)</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E75" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>Expenses Form</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>Expense_date</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>📅 date of expense</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Date of expense</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
         <is>
           <t>Date Picker</t>
         </is>
       </c>
-      <c r="E76" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="E77" s="4" t="n"/>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>Expenses Form</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>City_name</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>🏙️ city</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
         <is>
           <t>Selector (Dropdown)</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>["Bengaluru", "Mumbai"]</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>Expenses Form</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>Expense_type</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>🔄 expense type</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Expense type</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>Selector (Radio)</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>["Capital Expense (Capex)", "Operational Expense (Opex)"]</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>Expenses Form</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>📁 expense category</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Expense category</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
         <is>
           <t>Selector (Dropdown)</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="4" t="inlineStr">
         <is>
           <t>Dynamic (by Type)</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>Expenses Form</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>Vehicle_number</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>🚗 vehicle number (if applicable)</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Vehicle number (if applicable)</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E80" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="E81" s="4" t="n"/>
+      <c r="F81" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>Expenses Form</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>💵 amount (inr)</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Amount (inr)</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Number)</t>
         </is>
       </c>
-      <c r="E81" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="22" customHeight="1">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="E82" s="4" t="n"/>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>Expenses Form</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>📝 detailed remarks</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Detailed remarks</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E82" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="22" customHeight="1">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="E83" s="4" t="n"/>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>Expenses Form</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>Invoice_proof_url</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>📎 invoice / bill proof</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Invoice / bill proof</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>Photo/File Upload</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>PDF/Image</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>Expenses Form</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>Approved_by</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>👤 approved by (name)</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Approved by (name)</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E84" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>Expenses Form</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>Paid_to</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>👤 paid to (vendor / person)</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Paid to (vendor / person)</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E85" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="E86" s="4" t="n"/>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>Expenses Form</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>Submitting_user</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>🔑 submitted by (user)</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Submitted by (user)</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>Data Entry (Text)</t>
         </is>
       </c>
-      <c r="E86" s="2" t="n">
-        <v/>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="E87" s="4" t="n"/>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="4" t="n"/>
+      <c r="B88" s="4" t="n"/>
+      <c r="C88" s="4" t="n"/>
+      <c r="D88" s="4" t="n"/>
+      <c r="E88" s="4" t="n"/>
+      <c r="F88" s="4" t="n"/>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="4" t="n"/>
+      <c r="B89" s="4" t="n"/>
+      <c r="C89" s="4" t="n"/>
+      <c r="D89" s="4" t="n"/>
+      <c r="E89" s="4" t="n"/>
+      <c r="F89" s="4" t="n"/>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="4" t="n"/>
+      <c r="B90" s="4" t="n"/>
+      <c r="C90" s="4" t="n"/>
+      <c r="D90" s="4" t="n"/>
+      <c r="E90" s="4" t="n"/>
+      <c r="F90" s="4" t="n"/>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="4" t="n"/>
+      <c r="B91" s="4" t="n"/>
+      <c r="C91" s="4" t="n"/>
+      <c r="D91" s="4" t="n"/>
+      <c r="E91" s="4" t="n"/>
+      <c r="F91" s="4" t="n"/>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="4" t="n"/>
+      <c r="B92" s="4" t="n"/>
+      <c r="C92" s="4" t="n"/>
+      <c r="D92" s="4" t="n"/>
+      <c r="E92" s="4" t="n"/>
+      <c r="F92" s="4" t="n"/>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="4" t="n"/>
+      <c r="B93" s="4" t="n"/>
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="4" t="n"/>
+      <c r="E93" s="4" t="n"/>
+      <c r="F93" s="4" t="n"/>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="4" t="n"/>
+      <c r="B94" s="4" t="n"/>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="n"/>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="n"/>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="4" t="n"/>
+      <c r="B95" s="4" t="n"/>
+      <c r="C95" s="4" t="n"/>
+      <c r="D95" s="4" t="n"/>
+      <c r="E95" s="4" t="n"/>
+      <c r="F95" s="4" t="n"/>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="4" t="n"/>
+      <c r="B96" s="4" t="n"/>
+      <c r="C96" s="4" t="n"/>
+      <c r="D96" s="4" t="n"/>
+      <c r="E96" s="4" t="n"/>
+      <c r="F96" s="4" t="n"/>
+    </row>
+    <row r="97" ht="22" customHeight="1">
+      <c r="A97" s="4" t="n"/>
+      <c r="B97" s="4" t="n"/>
+      <c r="C97" s="4" t="n"/>
+      <c r="D97" s="4" t="n"/>
+      <c r="E97" s="4" t="n"/>
+      <c r="F97" s="4" t="n"/>
+    </row>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="4" t="n"/>
+      <c r="B98" s="4" t="n"/>
+      <c r="C98" s="4" t="n"/>
+      <c r="D98" s="4" t="n"/>
+      <c r="E98" s="4" t="n"/>
+      <c r="F98" s="4" t="n"/>
+    </row>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="4" t="n"/>
+      <c r="B99" s="4" t="n"/>
+      <c r="C99" s="4" t="n"/>
+      <c r="D99" s="4" t="n"/>
+      <c r="E99" s="4" t="n"/>
+      <c r="F99" s="4" t="n"/>
+    </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="4" t="n"/>
+      <c r="B100" s="4" t="n"/>
+      <c r="C100" s="4" t="n"/>
+      <c r="D100" s="4" t="n"/>
+      <c r="E100" s="4" t="n"/>
+      <c r="F100" s="4" t="n"/>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="4" t="n"/>
+      <c r="B101" s="4" t="n"/>
+      <c r="C101" s="4" t="n"/>
+      <c r="D101" s="4" t="n"/>
+      <c r="E101" s="4" t="n"/>
+      <c r="F101" s="4" t="n"/>
+    </row>
+    <row r="102" ht="22" customHeight="1">
+      <c r="A102" s="4" t="n"/>
+      <c r="B102" s="4" t="n"/>
+      <c r="C102" s="4" t="n"/>
+      <c r="D102" s="4" t="n"/>
+      <c r="E102" s="4" t="n"/>
+      <c r="F102" s="4" t="n"/>
+    </row>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="4" t="n"/>
+      <c r="B103" s="4" t="n"/>
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="4" t="n"/>
+      <c r="E103" s="4" t="n"/>
+      <c r="F103" s="4" t="n"/>
+    </row>
+    <row r="104" ht="22" customHeight="1">
+      <c r="A104" s="4" t="n"/>
+      <c r="B104" s="4" t="n"/>
+      <c r="C104" s="4" t="n"/>
+      <c r="D104" s="4" t="n"/>
+      <c r="E104" s="4" t="n"/>
+      <c r="F104" s="4" t="n"/>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="A105" s="4" t="n"/>
+      <c r="B105" s="4" t="n"/>
+      <c r="C105" s="4" t="n"/>
+      <c r="D105" s="4" t="n"/>
+      <c r="E105" s="4" t="n"/>
+      <c r="F105" s="4" t="n"/>
+    </row>
+    <row r="106" ht="22" customHeight="1">
+      <c r="A106" s="4" t="n"/>
+      <c r="B106" s="4" t="n"/>
+      <c r="C106" s="4" t="n"/>
+      <c r="D106" s="4" t="n"/>
+      <c r="E106" s="4" t="n"/>
+      <c r="F106" s="4" t="n"/>
+    </row>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="4" t="n"/>
+      <c r="B107" s="4" t="n"/>
+      <c r="C107" s="4" t="n"/>
+      <c r="D107" s="4" t="n"/>
+      <c r="E107" s="4" t="n"/>
+      <c r="F107" s="4" t="n"/>
+    </row>
+    <row r="108" ht="22" customHeight="1">
+      <c r="A108" s="4" t="n"/>
+      <c r="B108" s="4" t="n"/>
+      <c r="C108" s="4" t="n"/>
+      <c r="D108" s="4" t="n"/>
+      <c r="E108" s="4" t="n"/>
+      <c r="F108" s="4" t="n"/>
+    </row>
+    <row r="109" ht="22" customHeight="1">
+      <c r="A109" s="4" t="n"/>
+      <c r="B109" s="4" t="n"/>
+      <c r="C109" s="4" t="n"/>
+      <c r="D109" s="4" t="n"/>
+      <c r="E109" s="4" t="n"/>
+      <c r="F109" s="4" t="n"/>
+    </row>
+    <row r="110" ht="22" customHeight="1">
+      <c r="A110" s="4" t="n"/>
+      <c r="B110" s="4" t="n"/>
+      <c r="C110" s="4" t="n"/>
+      <c r="D110" s="4" t="n"/>
+      <c r="E110" s="4" t="n"/>
+      <c r="F110" s="4" t="n"/>
+    </row>
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="4" t="n"/>
+      <c r="B111" s="4" t="n"/>
+      <c r="C111" s="4" t="n"/>
+      <c r="D111" s="4" t="n"/>
+      <c r="E111" s="4" t="n"/>
+      <c r="F111" s="4" t="n"/>
+    </row>
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="4" t="n"/>
+      <c r="B112" s="4" t="n"/>
+      <c r="C112" s="4" t="n"/>
+      <c r="D112" s="4" t="n"/>
+      <c r="E112" s="4" t="n"/>
+      <c r="F112" s="4" t="n"/>
+    </row>
+    <row r="113" ht="22" customHeight="1">
+      <c r="A113" s="4" t="n"/>
+      <c r="B113" s="4" t="n"/>
+      <c r="C113" s="4" t="n"/>
+      <c r="D113" s="4" t="n"/>
+      <c r="E113" s="4" t="n"/>
+      <c r="F113" s="4" t="n"/>
+    </row>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="4" t="n"/>
+      <c r="B114" s="4" t="n"/>
+      <c r="C114" s="4" t="n"/>
+      <c r="D114" s="4" t="n"/>
+      <c r="E114" s="4" t="n"/>
+      <c r="F114" s="4" t="n"/>
+    </row>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="4" t="n"/>
+      <c r="B115" s="4" t="n"/>
+      <c r="C115" s="4" t="n"/>
+      <c r="D115" s="4" t="n"/>
+      <c r="E115" s="4" t="n"/>
+      <c r="F115" s="4" t="n"/>
+    </row>
+    <row r="116" ht="22" customHeight="1">
+      <c r="A116" s="4" t="n"/>
+      <c r="B116" s="4" t="n"/>
+      <c r="C116" s="4" t="n"/>
+      <c r="D116" s="4" t="n"/>
+      <c r="E116" s="4" t="n"/>
+      <c r="F116" s="4" t="n"/>
+    </row>
+    <row r="117" ht="22" customHeight="1">
+      <c r="A117" s="4" t="n"/>
+      <c r="B117" s="4" t="n"/>
+      <c r="C117" s="4" t="n"/>
+      <c r="D117" s="4" t="n"/>
+      <c r="E117" s="4" t="n"/>
+      <c r="F117" s="4" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>